--- a/ransomware_merged.xlsx
+++ b/ransomware_merged.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Desktop\ITP\Project\datasets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8EEC1E45-7214-4A55-84DC-F3C927EFD9C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC012A6E-392E-4BFE-9826-483602C1F67A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3088" uniqueCount="2464">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3124" uniqueCount="2464">
   <si>
     <t>CVE-2009-3960</t>
   </si>
@@ -17980,7 +17980,9 @@
       <c r="B15" s="3" t="s">
         <v>759</v>
       </c>
-      <c r="C15" s="3"/>
+      <c r="C15" s="3" t="s">
+        <v>2</v>
+      </c>
       <c r="D15" s="3" t="s">
         <v>608</v>
       </c>
@@ -18103,7 +18105,9 @@
       <c r="B18" s="3" t="s">
         <v>770</v>
       </c>
-      <c r="C18" s="3"/>
+      <c r="C18" s="3" t="s">
+        <v>2</v>
+      </c>
       <c r="D18" s="3" t="s">
         <v>728</v>
       </c>
@@ -18431,7 +18435,9 @@
       <c r="B26" s="3" t="s">
         <v>792</v>
       </c>
-      <c r="C26" s="3"/>
+      <c r="C26" s="3" t="s">
+        <v>2</v>
+      </c>
       <c r="D26" s="3" t="s">
         <v>723</v>
       </c>
@@ -18554,7 +18560,9 @@
       <c r="B29" s="3" t="s">
         <v>802</v>
       </c>
-      <c r="C29" s="3"/>
+      <c r="C29" s="3" t="s">
+        <v>2</v>
+      </c>
       <c r="D29" s="3" t="s">
         <v>773</v>
       </c>
@@ -18593,7 +18601,9 @@
       <c r="B30" s="3" t="s">
         <v>805</v>
       </c>
-      <c r="C30" s="3"/>
+      <c r="C30" s="3" t="s">
+        <v>2</v>
+      </c>
       <c r="D30" s="3" t="s">
         <v>723</v>
       </c>
@@ -18798,7 +18808,9 @@
       <c r="B35" s="3" t="s">
         <v>820</v>
       </c>
-      <c r="C35" s="3"/>
+      <c r="C35" s="3" t="s">
+        <v>2</v>
+      </c>
       <c r="D35" s="3" t="s">
         <v>821</v>
       </c>
@@ -18962,7 +18974,9 @@
       <c r="B39" s="3" t="s">
         <v>835</v>
       </c>
-      <c r="C39" s="3"/>
+      <c r="C39" s="3" t="s">
+        <v>2</v>
+      </c>
       <c r="D39" s="3" t="s">
         <v>829</v>
       </c>
@@ -19001,7 +19015,9 @@
       <c r="B40" s="3" t="s">
         <v>837</v>
       </c>
-      <c r="C40" s="3"/>
+      <c r="C40" s="3" t="s">
+        <v>2</v>
+      </c>
       <c r="D40" s="3" t="s">
         <v>829</v>
       </c>
@@ -19333,7 +19349,9 @@
       <c r="B48" s="3" t="s">
         <v>859</v>
       </c>
-      <c r="C48" s="3"/>
+      <c r="C48" s="3" t="s">
+        <v>2</v>
+      </c>
       <c r="D48" s="3" t="s">
         <v>860</v>
       </c>
@@ -20245,7 +20263,9 @@
       <c r="B70" s="3" t="s">
         <v>938</v>
       </c>
-      <c r="C70" s="3"/>
+      <c r="C70" s="3" t="s">
+        <v>2</v>
+      </c>
       <c r="D70" s="3" t="s">
         <v>939</v>
       </c>
@@ -20489,7 +20509,9 @@
       <c r="B76" s="3" t="s">
         <v>321</v>
       </c>
-      <c r="C76" s="3"/>
+      <c r="C76" s="3" t="s">
+        <v>2</v>
+      </c>
       <c r="D76" s="3" t="s">
         <v>903</v>
       </c>
@@ -20835,7 +20857,9 @@
       <c r="B84" s="3" t="s">
         <v>973</v>
       </c>
-      <c r="C84" s="3"/>
+      <c r="C84" s="3" t="s">
+        <v>2</v>
+      </c>
       <c r="D84" s="3" t="s">
         <v>743</v>
       </c>
@@ -20915,7 +20939,9 @@
       <c r="B86" s="3" t="s">
         <v>333</v>
       </c>
-      <c r="C86" s="3"/>
+      <c r="C86" s="3" t="s">
+        <v>2</v>
+      </c>
       <c r="D86" s="3" t="s">
         <v>976</v>
       </c>
@@ -20999,7 +21025,9 @@
       <c r="B88" s="3" t="s">
         <v>335</v>
       </c>
-      <c r="C88" s="3"/>
+      <c r="C88" s="3" t="s">
+        <v>2</v>
+      </c>
       <c r="D88" s="3" t="s">
         <v>976</v>
       </c>
@@ -21544,7 +21572,9 @@
       <c r="B101" s="3" t="s">
         <v>1012</v>
       </c>
-      <c r="C101" s="3"/>
+      <c r="C101" s="3" t="s">
+        <v>2</v>
+      </c>
       <c r="D101" s="3" t="s">
         <v>1013</v>
       </c>
@@ -21667,7 +21697,9 @@
       <c r="B104" s="3" t="s">
         <v>1019</v>
       </c>
-      <c r="C104" s="3"/>
+      <c r="C104" s="3" t="s">
+        <v>2</v>
+      </c>
       <c r="D104" s="3" t="s">
         <v>1020</v>
       </c>
@@ -22019,7 +22051,9 @@
       <c r="B112" s="3" t="s">
         <v>1042</v>
       </c>
-      <c r="C112" s="3"/>
+      <c r="C112" s="3" t="s">
+        <v>2</v>
+      </c>
       <c r="D112" s="3" t="s">
         <v>1043</v>
       </c>
@@ -22148,7 +22182,9 @@
       <c r="B115" s="3" t="s">
         <v>1053</v>
       </c>
-      <c r="C115" s="3"/>
+      <c r="C115" s="3" t="s">
+        <v>2</v>
+      </c>
       <c r="D115" s="3" t="s">
         <v>1020</v>
       </c>
@@ -22187,7 +22223,9 @@
       <c r="B116" s="3" t="s">
         <v>1055</v>
       </c>
-      <c r="C116" s="3"/>
+      <c r="C116" s="3" t="s">
+        <v>2</v>
+      </c>
       <c r="D116" s="3" t="s">
         <v>1056</v>
       </c>
@@ -22773,7 +22811,9 @@
       <c r="B130" s="3" t="s">
         <v>349</v>
       </c>
-      <c r="C130" s="3"/>
+      <c r="C130" s="3" t="s">
+        <v>2</v>
+      </c>
       <c r="D130" s="3" t="s">
         <v>608</v>
       </c>
@@ -22988,7 +23028,9 @@
       <c r="B135" s="3" t="s">
         <v>357</v>
       </c>
-      <c r="C135" s="3"/>
+      <c r="C135" s="3" t="s">
+        <v>2</v>
+      </c>
       <c r="D135" s="3" t="s">
         <v>1056</v>
       </c>
@@ -23027,7 +23069,9 @@
       <c r="B136" s="3" t="s">
         <v>359</v>
       </c>
-      <c r="C136" s="3"/>
+      <c r="C136" s="3" t="s">
+        <v>2</v>
+      </c>
       <c r="D136" s="3" t="s">
         <v>1056</v>
       </c>
@@ -23111,7 +23155,9 @@
       <c r="B138" s="3" t="s">
         <v>1118</v>
       </c>
-      <c r="C138" s="3"/>
+      <c r="C138" s="3" t="s">
+        <v>2</v>
+      </c>
       <c r="D138" s="3" t="s">
         <v>1119</v>
       </c>
@@ -23150,7 +23196,9 @@
       <c r="B139" s="3" t="s">
         <v>1122</v>
       </c>
-      <c r="C139" s="3"/>
+      <c r="C139" s="3" t="s">
+        <v>2</v>
+      </c>
       <c r="D139" s="3" t="s">
         <v>1119</v>
       </c>
@@ -23277,7 +23325,9 @@
       <c r="B142" s="3" t="s">
         <v>1129</v>
       </c>
-      <c r="C142" s="3"/>
+      <c r="C142" s="3" t="s">
+        <v>2</v>
+      </c>
       <c r="D142" s="3" t="s">
         <v>1130</v>
       </c>
@@ -23656,7 +23706,9 @@
       <c r="B151" s="3" t="s">
         <v>373</v>
       </c>
-      <c r="C151" s="3"/>
+      <c r="C151" s="3" t="s">
+        <v>2</v>
+      </c>
       <c r="D151" s="3" t="s">
         <v>1156</v>
       </c>
@@ -23865,7 +23917,9 @@
       <c r="B156" s="3" t="s">
         <v>381</v>
       </c>
-      <c r="C156" s="3"/>
+      <c r="C156" s="3" t="s">
+        <v>2</v>
+      </c>
       <c r="D156" s="3" t="s">
         <v>976</v>
       </c>
@@ -24037,7 +24091,9 @@
       <c r="B160" s="3" t="s">
         <v>385</v>
       </c>
-      <c r="C160" s="3"/>
+      <c r="C160" s="3" t="s">
+        <v>2</v>
+      </c>
       <c r="D160" s="3" t="s">
         <v>743</v>
       </c>
@@ -24690,7 +24746,9 @@
       <c r="B175" s="3" t="s">
         <v>393</v>
       </c>
-      <c r="C175" s="3"/>
+      <c r="C175" s="3" t="s">
+        <v>2</v>
+      </c>
       <c r="D175" s="3" t="s">
         <v>743</v>
       </c>
@@ -28706,7 +28764,9 @@
       <c r="B268" s="3" t="s">
         <v>1489</v>
       </c>
-      <c r="C268" s="3"/>
+      <c r="C268" s="3" t="s">
+        <v>2</v>
+      </c>
       <c r="D268" s="3" t="s">
         <v>1490</v>
       </c>
@@ -35909,7 +35969,9 @@
       <c r="B435" s="3" t="s">
         <v>411</v>
       </c>
-      <c r="C435" s="3"/>
+      <c r="C435" s="3" t="s">
+        <v>2</v>
+      </c>
       <c r="D435" s="3" t="s">
         <v>1970</v>
       </c>
@@ -35946,7 +36008,9 @@
       <c r="B436" s="3" t="s">
         <v>411</v>
       </c>
-      <c r="C436" s="3"/>
+      <c r="C436" s="3" t="s">
+        <v>2</v>
+      </c>
       <c r="D436" s="3" t="s">
         <v>1970</v>
       </c>
@@ -37387,8 +37451,12 @@
       <c r="A470" s="3" t="s">
         <v>639</v>
       </c>
-      <c r="B470" s="3"/>
-      <c r="C470" s="3"/>
+      <c r="B470" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C470" s="3" t="s">
+        <v>2</v>
+      </c>
       <c r="D470" s="3" t="s">
         <v>773</v>
       </c>
@@ -37422,8 +37490,12 @@
       <c r="A471" s="3" t="s">
         <v>638</v>
       </c>
-      <c r="B471" s="3"/>
-      <c r="C471" s="3"/>
+      <c r="B471" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C471" s="3" t="s">
+        <v>2</v>
+      </c>
       <c r="D471" s="3" t="s">
         <v>773</v>
       </c>
